--- a/ManualTestingSauceDemo.xlsx
+++ b/ManualTestingSauceDemo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Manual Testing Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822351B1-3FCE-4007-A172-7E8B86CEBB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA89638-636E-4EFB-A815-329F5FFC289A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{0AE3414F-58F0-44CB-A31B-623FB65EC7B1}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="378">
   <si>
     <t>Scenario Id</t>
   </si>
@@ -1320,12 +1320,21 @@
   <si>
     <t>Remove one product from cart page when multiple products are in the cart.</t>
   </si>
+  <si>
+    <t>Evidence\Bug_001_InvalidPostal_code.png</t>
+  </si>
+  <si>
+    <t>Evidence\Bug_002_OrderConfirmation.png</t>
+  </si>
+  <si>
+    <t>Evidence\Bug_003_Reset_app.png</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1344,6 +1353,14 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1387,10 +1404,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1412,8 +1430,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4619,13 +4644,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39FE6020-1ECE-41EE-B38A-987503C41C74}">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultColWidth="24.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="24.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>333</v>
       </c>
@@ -4672,7 +4697,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>341</v>
       </c>
@@ -4715,9 +4740,12 @@
       <c r="N2" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="O2" s="5"/>
-    </row>
-    <row r="3" spans="1:15" ht="144" x14ac:dyDescent="0.3">
+      <c r="O2" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="P2" s="10"/>
+    </row>
+    <row r="3" spans="1:16" ht="144" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>344</v>
       </c>
@@ -4760,9 +4788,11 @@
       <c r="N3" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="O3" s="5"/>
-    </row>
-    <row r="4" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="O3" s="9" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>346</v>
       </c>
@@ -4805,10 +4835,17 @@
       <c r="N4" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="O4" s="5"/>
+      <c r="O4" s="9" t="s">
+        <v>377</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="O2" r:id="rId1" xr:uid="{7DA2FB9C-C2C2-430A-94DF-7C614C101C3D}"/>
+    <hyperlink ref="O3" r:id="rId2" xr:uid="{408499FB-F6D7-4B2C-A7D1-9801550C4F43}"/>
+    <hyperlink ref="O4" r:id="rId3" xr:uid="{436C1C52-5F73-4A10-9ED6-5E4D3D1A8E48}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>